--- a/reports/daily_revenue.xlsx
+++ b/reports/daily_revenue.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Daily Performance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sources &amp; Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$53</definedName>
@@ -2756,13 +2756,13 @@
         <v>11525.74</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>6926.65003</v>
+        <v>7081.19002</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>2339.34</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1399.62</v>
+        <v>1399.66</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>140</v>
@@ -2771,10 +2771,10 @@
         <v>139.328</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>9265.990030000001</v>
+        <v>9420.53002</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>-1146.40003</v>
+        <v>-1300.94002</v>
       </c>
       <c r="K53" s="3" t="n">
         <v>30000</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>469804.30923</v>
+        <v>469958.84922</v>
       </c>
     </row>
     <row r="5">
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>551783.56907</v>
+        <v>551938.10906</v>
       </c>
     </row>
     <row r="7">
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>82585.38093</v>
+        <v>82430.84093999999</v>
       </c>
     </row>
     <row r="8">
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>126869.64</v>
+        <v>126869.68</v>
       </c>
     </row>
     <row r="9">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>5.019087072368141</v>
+        <v>5.019085489929509</v>
       </c>
     </row>
     <row r="12">
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.3695932645573097</v>
+        <v>0.369714840580106</v>
       </c>
     </row>
     <row r="16">
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0.4340860367073076</v>
+        <v>0.4342076127301039</v>
       </c>
     </row>
     <row r="18">
@@ -2984,7 +2984,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.06496960530790849</v>
+        <v>0.06484802928511217</v>
       </c>
     </row>
   </sheetData>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>2026-04-24T15:18:09-05:00</t>
+          <t>2026-04-24T15:45:19-05:00</t>
         </is>
       </c>
     </row>

--- a/reports/daily_revenue.xlsx
+++ b/reports/daily_revenue.xlsx
@@ -2762,7 +2762,7 @@
         <v>2339.34</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1399.66</v>
+        <v>1399.76</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>140</v>
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>126869.68</v>
+        <v>126869.78</v>
       </c>
     </row>
     <row r="9">
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>5.019085489929509</v>
+        <v>5.019081533837293</v>
       </c>
     </row>
     <row r="12">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>2026-04-24T15:45:19-05:00</t>
+          <t>2026-04-24T16:31:01-05:00</t>
         </is>
       </c>
     </row>

--- a/reports/daily_revenue.xlsx
+++ b/reports/daily_revenue.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sources &amp; Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2719,7 +2719,7 @@
         <v>267.18999</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1153.26</v>
+        <v>1153.28</v>
       </c>
       <c r="G52" s="4" t="n">
         <v>95</v>
@@ -2756,13 +2756,13 @@
         <v>11525.74</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>7081.19002</v>
+        <v>8058.03003</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>2339.34</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1399.76</v>
+        <v>1400.39</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>140</v>
@@ -2771,10 +2771,10 @@
         <v>139.328</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>9420.53002</v>
+        <v>10397.37003</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>-1300.94002</v>
+        <v>-2277.78003</v>
       </c>
       <c r="K53" s="3" t="n">
         <v>30000</v>
@@ -2786,8 +2786,51 @@
         <v>85</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>20042.77</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>12709.92</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>4376.54998</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>1128.49999</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>2565.74</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>143</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>138.681</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>5505.04997</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>1827.80003</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>-9957.23</v>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M53"/>
+  <autoFilter ref="A1:M54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2824,7 +2867,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>1271138.72</v>
+        <v>1291181.49</v>
       </c>
     </row>
     <row r="3">
@@ -2834,7 +2877,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>636769.77</v>
+        <v>649479.6899999999</v>
       </c>
     </row>
     <row r="4">
@@ -2844,7 +2887,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>469958.84922</v>
+        <v>475312.23921</v>
       </c>
     </row>
     <row r="5">
@@ -2854,7 +2897,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>81979.25984</v>
+        <v>83107.75983</v>
       </c>
     </row>
     <row r="6">
@@ -2864,7 +2907,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>551938.10906</v>
+        <v>558419.99904</v>
       </c>
     </row>
     <row r="7">
@@ -2874,7 +2917,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>82430.84093999999</v>
+        <v>83281.80095999999</v>
       </c>
     </row>
     <row r="8">
@@ -2884,7 +2927,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>126869.78</v>
+        <v>129436.17</v>
       </c>
     </row>
     <row r="9">
@@ -2894,7 +2937,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>9501</v>
+        <v>9644</v>
       </c>
     </row>
     <row r="10">
@@ -2904,7 +2947,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>133.7899926323545</v>
+        <v>133.8844348817918</v>
       </c>
     </row>
     <row r="11">
@@ -2914,7 +2957,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>5.019081533837293</v>
+        <v>5.017760414264421</v>
       </c>
     </row>
     <row r="12">
@@ -2924,7 +2967,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>1560000</v>
+        <v>1590000</v>
       </c>
     </row>
     <row r="13">
@@ -2934,7 +2977,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-288861.28</v>
+        <v>-298818.51</v>
       </c>
     </row>
     <row r="14">
@@ -2944,7 +2987,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.5009443579847839</v>
+        <v>0.5030119274711722</v>
       </c>
     </row>
     <row r="15">
@@ -2954,7 +2997,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.369714840580106</v>
+        <v>0.3681219432676346</v>
       </c>
     </row>
     <row r="16">
@@ -2964,7 +3007,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.06449277214999792</v>
+        <v>0.06436566855523929</v>
       </c>
     </row>
     <row r="17">
@@ -2974,7 +3017,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0.4342076127301039</v>
+        <v>0.4324876118228739</v>
       </c>
     </row>
     <row r="18">
@@ -2984,7 +3027,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.06484802928511217</v>
+        <v>0.06450046070595389</v>
       </c>
     </row>
   </sheetData>
@@ -3025,7 +3068,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>2026-04-24T16:31:01-05:00</t>
+          <t>2026-04-25T09:43:39-05:00</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3080,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>2026-03-03 through 2026-04-23</t>
+          <t>2026-03-03 through 2026-04-24</t>
         </is>
       </c>
     </row>

--- a/reports/daily_revenue.xlsx
+++ b/reports/daily_revenue.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sources &amp; Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2756,13 +2756,13 @@
         <v>11525.74</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>8058.03003</v>
+        <v>9120.470020000001</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>2339.34</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1400.39</v>
+        <v>1400.4</v>
       </c>
       <c r="G53" s="4" t="n">
         <v>140</v>
@@ -2771,10 +2771,10 @@
         <v>139.328</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>10397.37003</v>
+        <v>11459.81002</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>-2277.78003</v>
+        <v>-3340.22002</v>
       </c>
       <c r="K53" s="3" t="n">
         <v>30000</v>
@@ -2799,13 +2799,13 @@
         <v>12709.92</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>4376.54998</v>
+        <v>6454.91</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>1128.49999</v>
+        <v>985.24999</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2565.74</v>
+        <v>2575.84</v>
       </c>
       <c r="G54" s="4" t="n">
         <v>143</v>
@@ -2814,10 +2814,10 @@
         <v>138.681</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>5505.04997</v>
+        <v>7440.15999</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>1827.80003</v>
+        <v>-107.30999</v>
       </c>
       <c r="K54" s="3" t="n">
         <v>30000</v>
@@ -2829,8 +2829,51 @@
         <v>95</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>29836.02</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>21424.99</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>7517.48993</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>1454.54001</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>4341.27</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>140.884</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>8972.02994</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>-560.99994</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>-163.98</v>
+      </c>
+      <c r="M55" s="4" t="n">
+        <v>156</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M54"/>
+  <autoFilter ref="A1:M55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2867,7 +2910,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>1291181.49</v>
+        <v>1321017.51</v>
       </c>
     </row>
     <row r="3">
@@ -2877,7 +2920,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>649479.6899999999</v>
+        <v>670904.6800000001</v>
       </c>
     </row>
     <row r="4">
@@ -2887,7 +2930,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>475312.23921</v>
+        <v>485970.52915</v>
       </c>
     </row>
     <row r="5">
@@ -2897,7 +2940,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>83107.75983</v>
+        <v>84419.04984000001</v>
       </c>
     </row>
     <row r="6">
@@ -2907,7 +2950,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>558419.99904</v>
+        <v>570389.57899</v>
       </c>
     </row>
     <row r="7">
@@ -2917,7 +2960,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>83281.80095999999</v>
+        <v>79723.25101000001</v>
       </c>
     </row>
     <row r="8">
@@ -2927,7 +2970,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>129436.17</v>
+        <v>133787.55</v>
       </c>
     </row>
     <row r="9">
@@ -2937,7 +2980,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>9644</v>
+        <v>9854</v>
       </c>
     </row>
     <row r="10">
@@ -2947,7 +2990,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>133.8844348817918</v>
+        <v>134.0590125837223</v>
       </c>
     </row>
     <row r="11">
@@ -2957,7 +3000,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>5.017760414264421</v>
+        <v>5.014701891169993</v>
       </c>
     </row>
     <row r="12">
@@ -2967,7 +3010,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>1590000</v>
+        <v>1620000</v>
       </c>
     </row>
     <row r="13">
@@ -2977,7 +3020,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-298818.51</v>
+        <v>-298982.49</v>
       </c>
     </row>
     <row r="14">
@@ -2987,7 +3030,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.5030119274711722</v>
+        <v>0.5078696345213471</v>
       </c>
     </row>
     <row r="15">
@@ -2997,7 +3040,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.3681219432676346</v>
+        <v>0.3678759179732599</v>
       </c>
     </row>
     <row r="16">
@@ -3007,7 +3050,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.06436566855523929</v>
+        <v>0.06390456538308868</v>
       </c>
     </row>
     <row r="17">
@@ -3017,7 +3060,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0.4324876118228739</v>
+        <v>0.4317804833563486</v>
       </c>
     </row>
     <row r="18">
@@ -3027,7 +3070,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.06450046070595389</v>
+        <v>0.06034988212230434</v>
       </c>
     </row>
   </sheetData>
@@ -3068,7 +3111,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>2026-04-25T09:43:39-05:00</t>
+          <t>2026-04-26T09:46:17-05:00</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3123,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>2026-03-03 through 2026-04-24</t>
+          <t>2026-03-03 through 2026-04-25</t>
         </is>
       </c>
     </row>

--- a/reports/daily_revenue.xlsx
+++ b/reports/daily_revenue.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sources &amp; Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2756,7 +2756,7 @@
         <v>11525.74</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>9120.470020000001</v>
+        <v>9340.650009999999</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>2339.34</v>
@@ -2771,10 +2771,10 @@
         <v>139.328</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>11459.81002</v>
+        <v>11679.99001</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>-3340.22002</v>
+        <v>-3560.40001</v>
       </c>
       <c r="K53" s="3" t="n">
         <v>30000</v>
@@ -2799,13 +2799,13 @@
         <v>12709.92</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>6454.91</v>
+        <v>7146.42999</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>985.24999</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2575.84</v>
+        <v>2576.16</v>
       </c>
       <c r="G54" s="4" t="n">
         <v>143</v>
@@ -2814,10 +2814,10 @@
         <v>138.681</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>7440.15999</v>
+        <v>8131.67998</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>-107.30999</v>
+        <v>-798.82998</v>
       </c>
       <c r="K54" s="3" t="n">
         <v>30000</v>
@@ -2842,13 +2842,13 @@
         <v>21424.99</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>7517.48993</v>
+        <v>9924.76993</v>
       </c>
       <c r="E55" s="3" t="n">
         <v>1454.54001</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>4341.27</v>
+        <v>4348.84</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>210</v>
@@ -2857,10 +2857,10 @@
         <v>140.884</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>8972.02994</v>
+        <v>11379.30994</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-560.99994</v>
+        <v>-2968.27994</v>
       </c>
       <c r="K55" s="3" t="n">
         <v>30000</v>
@@ -2872,8 +2872,51 @@
         <v>156</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>34703.37</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>21355.13</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>12602.39004</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>3496.88999</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>3234.85</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>228</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>150.491</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>16099.28003</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>-2751.04003</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>4703.37</v>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>144</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M55"/>
+  <autoFilter ref="A1:M56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2910,7 +2953,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>1321017.51</v>
+        <v>1355720.88</v>
       </c>
     </row>
     <row r="3">
@@ -2920,7 +2963,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>670904.6800000001</v>
+        <v>692259.8100000001</v>
       </c>
     </row>
     <row r="4">
@@ -2930,7 +2973,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>485970.52915</v>
+        <v>501891.89917</v>
       </c>
     </row>
     <row r="5">
@@ -2940,7 +2983,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>84419.04984000001</v>
+        <v>87915.93983</v>
       </c>
     </row>
     <row r="6">
@@ -2950,7 +2993,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>570389.57899</v>
+        <v>589807.839</v>
       </c>
     </row>
     <row r="7">
@@ -2960,7 +3003,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>79723.25101000001</v>
+        <v>73653.231</v>
       </c>
     </row>
     <row r="8">
@@ -2970,7 +3013,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>133787.55</v>
+        <v>137030.29</v>
       </c>
     </row>
     <row r="9">
@@ -2980,7 +3023,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>9854</v>
+        <v>10082</v>
       </c>
     </row>
     <row r="10">
@@ -2990,7 +3033,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>134.0590125837223</v>
+        <v>134.4694386034517</v>
       </c>
     </row>
     <row r="11">
@@ -3000,7 +3043,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>5.014701891169993</v>
+        <v>5.051874370257845</v>
       </c>
     </row>
     <row r="12">
@@ -3010,7 +3053,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>1620000</v>
+        <v>1650000</v>
       </c>
     </row>
     <row r="13">
@@ -3020,7 +3063,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-298982.49</v>
+        <v>-294279.12</v>
       </c>
     </row>
     <row r="14">
@@ -3030,7 +3073,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.5078696345213471</v>
+        <v>0.5106211906981915</v>
       </c>
     </row>
     <row r="15">
@@ -3040,7 +3083,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.3678759179732599</v>
+        <v>0.3702029721412862</v>
       </c>
     </row>
     <row r="16">
@@ -3050,7 +3093,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.06390456538308868</v>
+        <v>0.06484811226777004</v>
       </c>
     </row>
     <row r="17">
@@ -3060,7 +3103,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0.4317804833563486</v>
+        <v>0.4350510844090562</v>
       </c>
     </row>
     <row r="18">
@@ -3070,7 +3113,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.06034988212230434</v>
+        <v>0.05432772489275226</v>
       </c>
     </row>
   </sheetData>
@@ -3111,7 +3154,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>2026-04-26T09:46:17-05:00</t>
+          <t>2026-04-27T10:50:19-05:00</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3166,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>2026-03-03 through 2026-04-25</t>
+          <t>2026-03-03 through 2026-04-26</t>
         </is>
       </c>
     </row>

--- a/reports/daily_revenue.xlsx
+++ b/reports/daily_revenue.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sources &amp; Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2756,7 +2756,7 @@
         <v>11525.74</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>9340.650009999999</v>
+        <v>9511.650009999999</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>2339.34</v>
@@ -2771,10 +2771,10 @@
         <v>139.328</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>11679.99001</v>
+        <v>11850.99001</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>-3560.40001</v>
+        <v>-3731.40001</v>
       </c>
       <c r="K53" s="3" t="n">
         <v>30000</v>
@@ -2842,13 +2842,13 @@
         <v>21424.99</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>9924.76993</v>
+        <v>10454.54993</v>
       </c>
       <c r="E55" s="3" t="n">
         <v>1454.54001</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>4348.84</v>
+        <v>4348.87</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>210</v>
@@ -2857,10 +2857,10 @@
         <v>140.884</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>11379.30994</v>
+        <v>11909.08994</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-2968.27994</v>
+        <v>-3498.05994</v>
       </c>
       <c r="K55" s="3" t="n">
         <v>30000</v>
@@ -2885,13 +2885,13 @@
         <v>21355.13</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>12602.39004</v>
+        <v>15299.24001</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>3496.88999</v>
+        <v>3748.56999</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>3234.85</v>
+        <v>3239.83</v>
       </c>
       <c r="G56" s="4" t="n">
         <v>228</v>
@@ -2900,10 +2900,10 @@
         <v>150.491</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>16099.28003</v>
+        <v>19047.81</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-2751.04003</v>
+        <v>-5699.57</v>
       </c>
       <c r="K56" s="3" t="n">
         <v>30000</v>
@@ -2915,8 +2915,51 @@
         <v>144</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>18557.44</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>13081.76</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>2387.12001</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>653.9100100000001</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>3093.34</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>135.813</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>3041.03002</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>2434.64998</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>-11442.56</v>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M56"/>
+  <autoFilter ref="A1:M57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2953,7 +2996,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>1355720.88</v>
+        <v>1374278.32</v>
       </c>
     </row>
     <row r="3">
@@ -2963,7 +3006,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>692259.8100000001</v>
+        <v>705341.5699999999</v>
       </c>
     </row>
     <row r="4">
@@ -2973,7 +3016,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>501891.89917</v>
+        <v>507676.64915</v>
       </c>
     </row>
     <row r="5">
@@ -2983,7 +3026,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>87915.93983</v>
+        <v>88821.52984</v>
       </c>
     </row>
     <row r="6">
@@ -2993,7 +3036,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>589807.839</v>
+        <v>596498.17899</v>
       </c>
     </row>
     <row r="7">
@@ -3003,7 +3046,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>73653.231</v>
+        <v>72438.57101</v>
       </c>
     </row>
     <row r="8">
@@ -3013,7 +3056,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>137030.29</v>
+        <v>140128.64</v>
       </c>
     </row>
     <row r="9">
@@ -3023,7 +3066,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>10082</v>
+        <v>10224</v>
       </c>
     </row>
     <row r="10">
@@ -3033,7 +3076,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>134.4694386034517</v>
+        <v>134.4168935837246</v>
       </c>
     </row>
     <row r="11">
@@ -3043,7 +3086,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>5.051874370257845</v>
+        <v>5.033528977373933</v>
       </c>
     </row>
     <row r="12">
@@ -3053,7 +3096,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>1650000</v>
+        <v>1680000</v>
       </c>
     </row>
     <row r="13">
@@ -3063,7 +3106,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-294279.12</v>
+        <v>-305721.68</v>
       </c>
     </row>
     <row r="14">
@@ -3073,7 +3116,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.5106211906981915</v>
+        <v>0.5132450681460216</v>
       </c>
     </row>
     <row r="15">
@@ -3083,7 +3126,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.3702029721412862</v>
+        <v>0.3694132707776399</v>
       </c>
     </row>
     <row r="16">
@@ -3093,7 +3136,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.06484811226777004</v>
+        <v>0.06463139856561224</v>
       </c>
     </row>
     <row r="17">
@@ -3103,7 +3146,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0.4350510844090562</v>
+        <v>0.4340446693432521</v>
       </c>
     </row>
     <row r="18">
@@ -3113,7 +3156,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.05432772489275226</v>
+        <v>0.05271026251072636</v>
       </c>
     </row>
   </sheetData>
@@ -3154,7 +3197,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>2026-04-27T10:50:19-05:00</t>
+          <t>2026-04-28T11:08:25-05:00</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3209,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>2026-03-03 through 2026-04-26</t>
+          <t>2026-03-03 through 2026-04-27</t>
         </is>
       </c>
     </row>

--- a/reports/daily_revenue.xlsx
+++ b/reports/daily_revenue.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sources &amp; Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2799,7 +2799,7 @@
         <v>12709.92</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>7146.42999</v>
+        <v>7488.42</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>985.24999</v>
@@ -2814,10 +2814,10 @@
         <v>138.681</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>8131.67998</v>
+        <v>8473.66999</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>-798.82998</v>
+        <v>-1140.81999</v>
       </c>
       <c r="K54" s="3" t="n">
         <v>30000</v>
@@ -2885,13 +2885,13 @@
         <v>21355.13</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>15299.24001</v>
+        <v>16535.54002</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>3748.56999</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>3239.83</v>
+        <v>3239.99</v>
       </c>
       <c r="G56" s="4" t="n">
         <v>228</v>
@@ -2900,10 +2900,10 @@
         <v>150.491</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>19047.81</v>
+        <v>20284.11001</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-5699.57</v>
+        <v>-6935.87001</v>
       </c>
       <c r="K56" s="3" t="n">
         <v>30000</v>
@@ -2928,13 +2928,13 @@
         <v>13081.76</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>2387.12001</v>
+        <v>2559.12001</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>653.9100100000001</v>
+        <v>788.74001</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>3093.34</v>
+        <v>3098.45</v>
       </c>
       <c r="G57" s="4" t="n">
         <v>142</v>
@@ -2943,10 +2943,10 @@
         <v>135.813</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>3041.03002</v>
+        <v>3347.86002</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>2434.64998</v>
+        <v>2127.81998</v>
       </c>
       <c r="K57" s="3" t="n">
         <v>30000</v>
@@ -2958,8 +2958,51 @@
         <v>95</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>17086.17</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>11482.12</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>2042.16001</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>759.7</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>2823.65</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>135.132</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>2801.86001</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>2802.18999</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>-12913.83</v>
+      </c>
+      <c r="M58" s="4" t="n">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M57"/>
+  <autoFilter ref="A1:M58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2996,7 +3039,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>1374278.32</v>
+        <v>1391364.49</v>
       </c>
     </row>
     <row r="3">
@@ -3006,7 +3049,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>705341.5699999999</v>
+        <v>716823.6899999999</v>
       </c>
     </row>
     <row r="4">
@@ -3016,7 +3059,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>507676.64915</v>
+        <v>511469.09918</v>
       </c>
     </row>
     <row r="5">
@@ -3026,7 +3069,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>88821.52984</v>
+        <v>89716.05984</v>
       </c>
     </row>
     <row r="6">
@@ -3036,7 +3079,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>596498.17899</v>
+        <v>601185.15902</v>
       </c>
     </row>
     <row r="7">
@@ -3046,7 +3089,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>72438.57101</v>
+        <v>73355.64098</v>
       </c>
     </row>
     <row r="8">
@@ -3056,7 +3099,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>140128.64</v>
+        <v>142957.56</v>
       </c>
     </row>
     <row r="9">
@@ -3066,7 +3109,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>10224</v>
+        <v>10355</v>
       </c>
     </row>
     <row r="10">
@@ -3076,7 +3119,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>134.4168935837246</v>
+        <v>134.3664403669725</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3129,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>5.033528977373933</v>
+        <v>5.014241219561946</v>
       </c>
     </row>
     <row r="12">
@@ -3096,7 +3139,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>1680000</v>
+        <v>1710000</v>
       </c>
     </row>
     <row r="13">
@@ -3106,7 +3149,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-305721.68</v>
+        <v>-318635.51</v>
       </c>
     </row>
     <row r="14">
@@ -3116,7 +3159,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.5132450681460216</v>
+        <v>0.5151947567671502</v>
       </c>
     </row>
     <row r="15">
@@ -3126,7 +3169,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.3694132707776399</v>
+        <v>0.3676025246123681</v>
       </c>
     </row>
     <row r="16">
@@ -3136,7 +3179,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.06463139856561224</v>
+        <v>0.06448063069368688</v>
       </c>
     </row>
     <row r="17">
@@ -3146,7 +3189,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0.4340446693432521</v>
+        <v>0.432083155306055</v>
       </c>
     </row>
     <row r="18">
@@ -3156,7 +3199,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.05271026251072636</v>
+        <v>0.05272208792679479</v>
       </c>
     </row>
   </sheetData>
@@ -3197,7 +3240,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>2026-04-28T11:08:25-05:00</t>
+          <t>2026-04-29T10:57:17-05:00</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3252,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>2026-03-03 through 2026-04-27</t>
+          <t>2026-03-03 through 2026-04-28</t>
         </is>
       </c>
     </row>

--- a/reports/daily_revenue.xlsx
+++ b/reports/daily_revenue.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sources &amp; Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$59</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2756,7 +2756,7 @@
         <v>11525.74</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>9511.650009999999</v>
+        <v>9666.190000000001</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>2339.34</v>
@@ -2771,10 +2771,10 @@
         <v>139.328</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>11850.99001</v>
+        <v>12005.53</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>-3731.40001</v>
+        <v>-3885.94</v>
       </c>
       <c r="K53" s="3" t="n">
         <v>30000</v>
@@ -2842,7 +2842,7 @@
         <v>21424.99</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>10454.54993</v>
+        <v>10629.88993</v>
       </c>
       <c r="E55" s="3" t="n">
         <v>1454.54001</v>
@@ -2857,10 +2857,10 @@
         <v>140.884</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>11909.08994</v>
+        <v>12084.42994</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>-3498.05994</v>
+        <v>-3673.39994</v>
       </c>
       <c r="K55" s="3" t="n">
         <v>30000</v>
@@ -2885,7 +2885,7 @@
         <v>21355.13</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>16535.54002</v>
+        <v>17595.72</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>3748.56999</v>
@@ -2900,10 +2900,10 @@
         <v>150.491</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>20284.11001</v>
+        <v>21344.28999</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-6935.87001</v>
+        <v>-7996.04999</v>
       </c>
       <c r="K56" s="3" t="n">
         <v>30000</v>
@@ -2928,13 +2928,13 @@
         <v>13081.76</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>2559.12001</v>
+        <v>2700.67001</v>
       </c>
       <c r="E57" s="3" t="n">
         <v>788.74001</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>3098.45</v>
+        <v>3098.55</v>
       </c>
       <c r="G57" s="4" t="n">
         <v>142</v>
@@ -2943,10 +2943,10 @@
         <v>135.813</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>3347.86002</v>
+        <v>3489.41002</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>2127.81998</v>
+        <v>1986.26998</v>
       </c>
       <c r="K57" s="3" t="n">
         <v>30000</v>
@@ -2971,13 +2971,13 @@
         <v>11482.12</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>2042.16001</v>
+        <v>3278.71</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>759.7</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>2823.65</v>
+        <v>2828.26</v>
       </c>
       <c r="G58" s="4" t="n">
         <v>131</v>
@@ -2986,10 +2986,10 @@
         <v>135.132</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>2801.86001</v>
+        <v>4038.41</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>2802.18999</v>
+        <v>1565.64</v>
       </c>
       <c r="K58" s="3" t="n">
         <v>30000</v>
@@ -3001,8 +3001,51 @@
         <v>82</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>19664.11</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>12275.31</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>2161.55001</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>1091.19</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>2987.39</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>143</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>136.021</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>3252.74001</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>4136.05999</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>-10335.89</v>
+      </c>
+      <c r="M59" s="4" t="n">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M58"/>
+  <autoFilter ref="A1:M59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3039,7 +3082,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>1391364.49</v>
+        <v>1411028.6</v>
       </c>
     </row>
     <row r="3">
@@ -3049,7 +3092,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>716823.6899999999</v>
+        <v>729099</v>
       </c>
     </row>
     <row r="4">
@@ -3059,7 +3102,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>511469.09918</v>
+        <v>516398.80915</v>
       </c>
     </row>
     <row r="5">
@@ -3069,7 +3112,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>89716.05984</v>
+        <v>90807.24984</v>
       </c>
     </row>
     <row r="6">
@@ -3079,7 +3122,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>601185.15902</v>
+        <v>607206.05899</v>
       </c>
     </row>
     <row r="7">
@@ -3089,7 +3132,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>73355.64098</v>
+        <v>74723.54101</v>
       </c>
     </row>
     <row r="8">
@@ -3099,7 +3142,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>142957.56</v>
+        <v>145949.66</v>
       </c>
     </row>
     <row r="9">
@@ -3109,7 +3152,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>10355</v>
+        <v>10498</v>
       </c>
     </row>
     <row r="10">
@@ -3119,7 +3162,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>134.3664403669725</v>
+        <v>134.4092779577062</v>
       </c>
     </row>
     <row r="11">
@@ -3129,7 +3172,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>5.014241219561946</v>
+        <v>4.995551205806167</v>
       </c>
     </row>
     <row r="12">
@@ -3139,7 +3182,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>1710000</v>
+        <v>1740000</v>
       </c>
     </row>
     <row r="13">
@@ -3149,7 +3192,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-318635.51</v>
+        <v>-328971.4</v>
       </c>
     </row>
     <row r="14">
@@ -3159,7 +3202,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.5151947567671502</v>
+        <v>0.5167145442693366</v>
       </c>
     </row>
     <row r="15">
@@ -3169,7 +3212,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.3676025246123681</v>
+        <v>0.3659733113488983</v>
       </c>
     </row>
     <row r="16">
@@ -3179,7 +3222,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.06448063069368688</v>
+        <v>0.0643553573896376</v>
       </c>
     </row>
     <row r="17">
@@ -3189,7 +3232,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0.432083155306055</v>
+        <v>0.4303286687385359</v>
       </c>
     </row>
     <row r="18">
@@ -3199,7 +3242,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.05272208792679479</v>
+        <v>0.05295678699212759</v>
       </c>
     </row>
   </sheetData>
@@ -3240,7 +3283,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>2026-04-29T10:57:17-05:00</t>
+          <t>2026-04-30T10:48:29-05:00</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3295,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>2026-03-03 through 2026-04-28</t>
+          <t>2026-03-03 through 2026-04-29</t>
         </is>
       </c>
     </row>

--- a/reports/daily_revenue.xlsx
+++ b/reports/daily_revenue.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sources &amp; Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2885,7 +2885,7 @@
         <v>21355.13</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>17595.72</v>
+        <v>17781.25999</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>3748.56999</v>
@@ -2900,10 +2900,10 @@
         <v>150.491</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>21344.28999</v>
+        <v>21529.82998</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-7996.04999</v>
+        <v>-8181.58998</v>
       </c>
       <c r="K56" s="3" t="n">
         <v>30000</v>
@@ -2971,7 +2971,7 @@
         <v>11482.12</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3278.71</v>
+        <v>3626.7</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>759.7</v>
@@ -2986,10 +2986,10 @@
         <v>135.132</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>4038.41</v>
+        <v>4386.4</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>1565.64</v>
+        <v>1217.65</v>
       </c>
       <c r="K58" s="3" t="n">
         <v>30000</v>
@@ -3014,13 +3014,13 @@
         <v>12275.31</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>2161.55001</v>
+        <v>2253.69001</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1091.19</v>
+        <v>1193.33</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>2987.39</v>
+        <v>2992.73</v>
       </c>
       <c r="G59" s="4" t="n">
         <v>143</v>
@@ -3029,10 +3029,10 @@
         <v>136.021</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>3252.74001</v>
+        <v>3447.02001</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>4136.05999</v>
+        <v>3941.77999</v>
       </c>
       <c r="K59" s="3" t="n">
         <v>30000</v>
@@ -3044,8 +3044,51 @@
         <v>84</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>22269.76</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>14087.74</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>6454.30002</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>1631.95999</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>2802.86</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>161</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>137.72</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>8086.26001</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>95.75999</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>-7730.24</v>
+      </c>
+      <c r="M60" s="4" t="n">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M59"/>
+  <autoFilter ref="A1:M60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3082,7 +3125,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>1411028.6</v>
+        <v>1433298.36</v>
       </c>
     </row>
     <row r="3">
@@ -3092,7 +3135,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>729099</v>
+        <v>743186.74</v>
       </c>
     </row>
     <row r="4">
@@ -3102,7 +3145,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>516398.80915</v>
+        <v>523478.77916</v>
       </c>
     </row>
     <row r="5">
@@ -3112,7 +3155,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>90807.24984</v>
+        <v>92541.34983000001</v>
       </c>
     </row>
     <row r="6">
@@ -3122,7 +3165,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>607206.05899</v>
+        <v>616020.12899</v>
       </c>
     </row>
     <row r="7">
@@ -3132,7 +3175,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>74723.54101</v>
+        <v>74091.49101</v>
       </c>
     </row>
     <row r="8">
@@ -3142,7 +3185,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>145949.66</v>
+        <v>148757.86</v>
       </c>
     </row>
     <row r="9">
@@ -3152,7 +3195,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>10498</v>
+        <v>10659</v>
       </c>
     </row>
     <row r="10">
@@ -3162,7 +3205,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>134.4092779577062</v>
+        <v>134.4683703912187</v>
       </c>
     </row>
     <row r="11">
@@ -3172,7 +3215,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>4.995551205806167</v>
+        <v>4.995949390506156</v>
       </c>
     </row>
     <row r="12">
@@ -3182,7 +3225,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>1740000</v>
+        <v>1770000</v>
       </c>
     </row>
     <row r="13">
@@ -3192,7 +3235,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-328971.4</v>
+        <v>-336701.64</v>
       </c>
     </row>
     <row r="14">
@@ -3202,7 +3245,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.5167145442693366</v>
+        <v>0.5185150285108817</v>
       </c>
     </row>
     <row r="15">
@@ -3212,7 +3255,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.3659733113488983</v>
+        <v>0.3652266644329377</v>
       </c>
     </row>
     <row r="16">
@@ -3222,7 +3265,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.0643553573896376</v>
+        <v>0.06456530783304601</v>
       </c>
     </row>
     <row r="17">
@@ -3232,7 +3275,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0.4303286687385359</v>
+        <v>0.4297919722659838</v>
       </c>
     </row>
     <row r="18">
@@ -3242,7 +3285,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.05295678699212759</v>
+        <v>0.05169299922313454</v>
       </c>
     </row>
   </sheetData>
@@ -3283,7 +3326,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>2026-04-30T10:48:29-05:00</t>
+          <t>2026-05-01T09:57:47-05:00</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3338,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>2026-03-03 through 2026-04-29</t>
+          <t>2026-03-03 through 2026-04-30</t>
         </is>
       </c>
     </row>

--- a/reports/daily_revenue.xlsx
+++ b/reports/daily_revenue.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sources &amp; Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2885,7 +2885,7 @@
         <v>21355.13</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>17781.25999</v>
+        <v>17867.25999</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>3748.56999</v>
@@ -2900,10 +2900,10 @@
         <v>150.491</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>21529.82998</v>
+        <v>21615.82998</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>-8181.58998</v>
+        <v>-8267.589980000001</v>
       </c>
       <c r="K56" s="3" t="n">
         <v>30000</v>
@@ -2971,7 +2971,7 @@
         <v>11482.12</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3626.7</v>
+        <v>4211.26</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>759.7</v>
@@ -2986,10 +2986,10 @@
         <v>135.132</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>4386.4</v>
+        <v>4970.96</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>1217.65</v>
+        <v>633.09</v>
       </c>
       <c r="K58" s="3" t="n">
         <v>30000</v>
@@ -3014,13 +3014,13 @@
         <v>12275.31</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>2253.69001</v>
+        <v>2458.62001</v>
       </c>
       <c r="E59" s="3" t="n">
         <v>1193.33</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>2992.73</v>
+        <v>2992.87</v>
       </c>
       <c r="G59" s="4" t="n">
         <v>143</v>
@@ -3029,10 +3029,10 @@
         <v>136.021</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>3447.02001</v>
+        <v>3651.95001</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>3941.77999</v>
+        <v>3736.84999</v>
       </c>
       <c r="K59" s="3" t="n">
         <v>30000</v>
@@ -3057,13 +3057,13 @@
         <v>14087.74</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>6454.30002</v>
+        <v>8036.07999</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>1631.95999</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>2802.86</v>
+        <v>2811.08</v>
       </c>
       <c r="G60" s="4" t="n">
         <v>161</v>
@@ -3072,10 +3072,10 @@
         <v>137.72</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>8086.26001</v>
+        <v>9668.03998</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>95.75999</v>
+        <v>-1486.01998</v>
       </c>
       <c r="K60" s="3" t="n">
         <v>30000</v>
@@ -3087,8 +3087,51 @@
         <v>102</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>30328.45</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>19177.9</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>5190.92999</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>3103.60999</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>3806.03</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>216</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>140.204</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>8294.53998</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>2856.01002</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>328.45</v>
+      </c>
+      <c r="M61" s="4" t="n">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M60"/>
+  <autoFilter ref="A1:M61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3125,7 +3168,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>1433298.36</v>
+        <v>1463626.81</v>
       </c>
     </row>
     <row r="3">
@@ -3135,7 +3178,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>743186.74</v>
+        <v>762364.64</v>
       </c>
     </row>
     <row r="4">
@@ -3145,7 +3188,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>523478.77916</v>
+        <v>531126.97912</v>
       </c>
     </row>
     <row r="5">
@@ -3155,7 +3198,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>92541.34983000001</v>
+        <v>95644.95982</v>
       </c>
     </row>
     <row r="6">
@@ -3165,7 +3208,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>616020.12899</v>
+        <v>626771.93894</v>
       </c>
     </row>
     <row r="7">
@@ -3175,7 +3218,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>74091.49101</v>
+        <v>74490.23106000001</v>
       </c>
     </row>
     <row r="8">
@@ -3185,7 +3228,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>148757.86</v>
+        <v>152572.25</v>
       </c>
     </row>
     <row r="9">
@@ -3195,7 +3238,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>10659</v>
+        <v>10875</v>
       </c>
     </row>
     <row r="10">
@@ -3205,7 +3248,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>134.4683703912187</v>
+        <v>134.5863733333333</v>
       </c>
     </row>
     <row r="11">
@@ -3215,7 +3258,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>4.995949390506156</v>
+        <v>4.996745083067203</v>
       </c>
     </row>
     <row r="12">
@@ -3225,7 +3268,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>1770000</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="13">
@@ -3235,7 +3278,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-336701.64</v>
+        <v>-336373.19</v>
       </c>
     </row>
     <row r="14">
@@ -3245,7 +3288,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.5185150285108817</v>
+        <v>0.5208736508454638</v>
       </c>
     </row>
     <row r="15">
@@ -3255,7 +3298,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.3652266644329377</v>
+        <v>0.3628841556407402</v>
       </c>
     </row>
     <row r="16">
@@ -3265,7 +3308,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.06456530783304601</v>
+        <v>0.0653479146231272</v>
       </c>
     </row>
     <row r="17">
@@ -3275,7 +3318,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0.4297919722659838</v>
+        <v>0.4282320702638673</v>
       </c>
     </row>
     <row r="18">
@@ -3285,7 +3328,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.05169299922313454</v>
+        <v>0.05089427889066886</v>
       </c>
     </row>
   </sheetData>
@@ -3326,7 +3369,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>2026-05-01T09:57:47-05:00</t>
+          <t>2026-05-02T09:50:54-05:00</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3381,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>2026-03-03 through 2026-04-30</t>
+          <t>2026-03-03 through 2026-05-01</t>
         </is>
       </c>
     </row>

--- a/reports/daily_revenue.xlsx
+++ b/reports/daily_revenue.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sources &amp; Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Performance'!$A$1:$M$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3057,13 +3057,13 @@
         <v>14087.74</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>8036.07999</v>
+        <v>8503.81999</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>1631.95999</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>2811.08</v>
+        <v>2811.26</v>
       </c>
       <c r="G60" s="4" t="n">
         <v>161</v>
@@ -3072,10 +3072,10 @@
         <v>137.72</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>9668.03998</v>
+        <v>10135.77998</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>-1486.01998</v>
+        <v>-1953.75998</v>
       </c>
       <c r="K60" s="3" t="n">
         <v>30000</v>
@@ -3100,13 +3100,13 @@
         <v>19177.9</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>5190.92999</v>
+        <v>5918.74998</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>3103.60999</v>
+        <v>3282.88</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>3806.03</v>
+        <v>3813.04</v>
       </c>
       <c r="G61" s="4" t="n">
         <v>216</v>
@@ -3115,10 +3115,10 @@
         <v>140.204</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>8294.53998</v>
+        <v>9201.62998</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>2856.01002</v>
+        <v>1948.92002</v>
       </c>
       <c r="K61" s="3" t="n">
         <v>30000</v>
@@ -3130,8 +3130,51 @@
         <v>136</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>23336.8</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>13713.7</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>4714.99996</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>2742.10002</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>2308.01</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>165</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>140.283</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>7457.09998</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>2166.00002</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>-6663.2</v>
+      </c>
+      <c r="M62" s="4" t="n">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M61"/>
+  <autoFilter ref="A1:M62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3168,7 +3211,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>1463626.81</v>
+        <v>1486963.61</v>
       </c>
     </row>
     <row r="3">
@@ -3178,7 +3221,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>762364.64</v>
+        <v>776078.34</v>
       </c>
     </row>
     <row r="4">
@@ -3188,7 +3231,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>531126.97912</v>
+        <v>537037.5390700001</v>
       </c>
     </row>
     <row r="5">
@@ -3198,7 +3241,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>95644.95982</v>
+        <v>98566.32984999999</v>
       </c>
     </row>
     <row r="6">
@@ -3208,7 +3251,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>626771.93894</v>
+        <v>635603.86892</v>
       </c>
     </row>
     <row r="7">
@@ -3218,7 +3261,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>74490.23106000001</v>
+        <v>75281.40108</v>
       </c>
     </row>
     <row r="8">
@@ -3228,7 +3271,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>152572.25</v>
+        <v>154887.45</v>
       </c>
     </row>
     <row r="9">
@@ -3238,7 +3281,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>10875</v>
+        <v>11040</v>
       </c>
     </row>
     <row r="10">
@@ -3248,7 +3291,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>134.5863733333333</v>
+        <v>134.6887327898551</v>
       </c>
     </row>
     <row r="11">
@@ -3258,7 +3301,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>4.996745083067203</v>
+        <v>5.010595371025865</v>
       </c>
     </row>
     <row r="12">
@@ -3268,7 +3311,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>1800000</v>
+        <v>1830000</v>
       </c>
     </row>
     <row r="13">
@@ -3278,7 +3321,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-336373.19</v>
+        <v>-343036.39</v>
       </c>
     </row>
     <row r="14">
@@ -3288,7 +3331,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.5208736508454638</v>
+        <v>0.5219215418459366</v>
       </c>
     </row>
     <row r="15">
@@ -3298,7 +3341,7 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>0.3628841556407402</v>
+        <v>0.3611638747971781</v>
       </c>
     </row>
     <row r="16">
@@ -3308,7 +3351,7 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>0.0653479146231272</v>
+        <v>0.06628698186501013</v>
       </c>
     </row>
     <row r="17">
@@ -3318,7 +3361,7 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>0.4282320702638673</v>
+        <v>0.4274508566621882</v>
       </c>
     </row>
     <row r="18">
@@ -3328,7 +3371,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.05089427889066886</v>
+        <v>0.05062760149187511</v>
       </c>
     </row>
   </sheetData>
@@ -3369,7 +3412,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>2026-05-02T09:50:54-05:00</t>
+          <t>2026-05-03T09:51:23-05:00</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3424,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>2026-03-03 through 2026-05-01</t>
+          <t>2026-03-03 through 2026-05-02</t>
         </is>
       </c>
     </row>
